--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488214_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488214_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4339</v>
+        <v>7.8004</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2539</v>
+        <v>2.1412</v>
       </c>
       <c r="F2" t="n">
-        <v>8.1799</v>
+        <v>5.6592</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9956</v>
+        <v>5.2014</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8419</v>
+        <v>2.0282</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1536</v>
+        <v>3.1732</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.5137</v>
+        <v>1.8664</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.7318</v>
+        <v>-0.1161</v>
       </c>
       <c r="L2" t="n">
-        <v>0.218</v>
+        <v>1.9824</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5093</v>
+        <v>3.335</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5737</v>
+        <v>2.1443</v>
       </c>
       <c r="O2" t="n">
-        <v>1.9356</v>
+        <v>1.1907</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0382</v>
+        <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5882</v>
+        <v>1.1167</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9557</v>
+        <v>0.2749</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6325</v>
+        <v>0.8418</v>
       </c>
       <c r="V2" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8774</v>
+        <v>6.7235</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1936</v>
+        <v>-0.6931</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6838</v>
+        <v>7.4167</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2014</v>
+        <v>2.9956</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0282</v>
+        <v>0.8419</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1732</v>
+        <v>2.1536</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8664</v>
+        <v>-1.5137</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1161</v>
+        <v>-1.7318</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9824</v>
+        <v>0.218</v>
       </c>
       <c r="M3" t="n">
-        <v>3.335</v>
+        <v>4.5093</v>
       </c>
       <c r="N3" t="n">
-        <v>2.1443</v>
+        <v>2.5737</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1907</v>
+        <v>1.9356</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4823</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1937</v>
+        <v>2.8778</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6727</v>
+        <v>2.0087</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8665</v>
+        <v>0.8692</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.439</v>
+        <v>5.0496</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3769</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>4.0621</v>
@@ -766,10 +766,10 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2064</v>
+        <v>0.4041</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1679</v>
+        <v>0.4427</v>
       </c>
       <c r="U4" t="n">
         <v>-0.0386</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.519</v>
+        <v>2.7269</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4042</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1148</v>
+        <v>2.2133</v>
       </c>
       <c r="G5" t="n">
         <v>1.1352</v>
@@ -844,13 +844,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8279</v>
+        <v>1.0359</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.092</v>
+        <v>0.0174</v>
       </c>
       <c r="U5" t="n">
-        <v>0.92</v>
+        <v>1.0184</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2441</v>
+        <v>1.3817</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2441</v>
+        <v>0.0513</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.3304</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2441</v>
+        <v>-0.321</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2.3873</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2441</v>
+        <v>-2.7083</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2441</v>
+        <v>-2.342</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2441</v>
+        <v>-2.5474</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.021</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.182</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.161</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.8885</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4707</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.4178</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.7755</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.1466</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1125</v>
+        <v>1.2441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0283</v>
+        <v>1.2441</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0842</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.321</v>
+        <v>1.2441</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3873</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.7083</v>
+        <v>1.2441</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.342</v>
+        <v>1.2441</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.5474</v>
+        <v>1.2441</v>
       </c>
       <c r="M7" t="n">
-        <v>2.021</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.182</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.161</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6193</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4477</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1716</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.7755</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.1466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3544</v>
+        <v>1.0287</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9035</v>
+        <v>-2.9322</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2579</v>
+        <v>3.9609</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1457</v>
+        <v>-0.1695</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9123</v>
+        <v>-0.6581</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2335</v>
+        <v>0.4886</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4285</v>
+        <v>-1.6296</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-1.7955</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1043</v>
+        <v>0.1659</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5742</v>
+        <v>1.4602</v>
       </c>
       <c r="N8" t="n">
-        <v>1.445</v>
+        <v>1.1374</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1292</v>
+        <v>0.3227</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7411</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2823</v>
+        <v>1.1982</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4514</v>
+        <v>0.5503</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1691</v>
+        <v>0.6479</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8883</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0076</v>
+        <v>0.471</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5745</v>
+        <v>-1.0331</v>
       </c>
       <c r="F9" t="n">
-        <v>3.567</v>
+        <v>1.5041</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1695</v>
+        <v>2.1457</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6581</v>
+        <v>0.9123</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4886</v>
+        <v>1.2335</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6296</v>
+        <v>-0.4285</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7955</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1659</v>
+        <v>0.1043</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4602</v>
+        <v>2.5742</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1374</v>
+        <v>1.445</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3227</v>
+        <v>1.1292</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1619</v>
+        <v>0.3989</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.092</v>
+        <v>0.3218</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2539</v>
+        <v>0.0771</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8883</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1848</v>
+        <v>0.0833</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3479</v>
+        <v>-2.8583</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1632</v>
+        <v>2.9416</v>
       </c>
       <c r="G10" t="n">
         <v>0.3831</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0436</v>
+        <v>1.3116</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2897</v>
+        <v>0.1999</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3333</v>
+        <v>1.1117</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3056</v>
+        <v>-0.3297</v>
       </c>
       <c r="E11" t="n">
-        <v>1.07</v>
+        <v>0.972</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3756</v>
+        <v>-1.3017</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3847</v>
@@ -1312,13 +1312,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1062</v>
+        <v>-0.1303</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1057</v>
+        <v>0.0078</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="V11" t="n">
         <v>0.6294</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9146</v>
+        <v>-0.5174</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2822</v>
+        <v>-0.8358</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3676</v>
+        <v>0.3184</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2187</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0664</v>
+        <v>0.3308</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0584</v>
+        <v>0.388</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.008</v>
+        <v>-0.0572</v>
       </c>
       <c r="V12" t="n">
         <v>1.2589</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.56770000000001</v>
+        <v>25.6621</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5371</v>
+        <v>-2.4429</v>
       </c>
       <c r="F13" t="n">
-        <v>28.1049</v>
+        <v>28.105</v>
       </c>
       <c r="G13" t="n">
         <v>12.1564</v>
@@ -1468,13 +1468,13 @@
         <v>12.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>8.337899999999999</v>
+        <v>9.4322</v>
       </c>
       <c r="T13" t="n">
-        <v>3.587800000000001</v>
+        <v>4.682200000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.7502</v>
+        <v>4.7501</v>
       </c>
       <c r="V13" t="n">
         <v>3.1472</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0996</v>
+        <v>1.2805</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3304</v>
+        <v>0.1345</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7692</v>
+        <v>1.146</v>
       </c>
       <c r="G14" t="n">
         <v>1.449</v>
@@ -1546,13 +1546,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9053</v>
+        <v>-0.7244</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1816</v>
+        <v>-0.0143</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0869</v>
+        <v>-0.7101</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. RAMOS MENDEZ</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0547</v>
+        <v>0.1929</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0547</v>
+        <v>-2.3037</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.4966</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.9385</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.5745</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.364</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.1855</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1043</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.753</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.4933</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.2597</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2234</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0547</v>
+        <v>-0.2633</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0547</v>
+        <v>-0.2658</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>I. RAMOS MENDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5515</v>
+        <v>-0.0547</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5975</v>
+        <v>-0.0547</v>
       </c>
       <c r="F18" t="n">
-        <v>2.046</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9385</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5745</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.364</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1855</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1043</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.753</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4933</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2597</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2234</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0078</v>
+        <v>-0.0547</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5596</v>
+        <v>-0.0547</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4482</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2054</v>
+        <v>-1.0313</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3233</v>
+        <v>-1.6171</v>
       </c>
       <c r="F19" t="n">
-        <v>0.118</v>
+        <v>0.5858</v>
       </c>
       <c r="G19" t="n">
         <v>1.2628</v>
@@ -1936,13 +1936,13 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8458</v>
+        <v>-0.6718</v>
       </c>
       <c r="T19" t="n">
-        <v>0.148</v>
+        <v>-0.1458</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9938</v>
+        <v>-0.526</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8812</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2593</v>
+        <v>-2.1614</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1977</v>
+        <v>-0.0998</v>
       </c>
       <c r="F20" t="n">
         <v>-2.0616</v>
@@ -2014,10 +2014,10 @@
         <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8506</v>
+        <v>-0.7526</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1977</v>
+        <v>-0.0998</v>
       </c>
       <c r="U20" t="n">
         <v>-0.6529</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9365</v>
+        <v>-2.5058</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.339</v>
+        <v>-3.8493</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4025</v>
+        <v>1.3435</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3413</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4731</v>
+        <v>-1.0424</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3927</v>
+        <v>-0.9031</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0804</v>
+        <v>-0.1393</v>
       </c>
       <c r="V21" t="n">
         <v>0.06320000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5107</v>
+        <v>-3.309</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5181</v>
+        <v>-3.0285</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0075</v>
+        <v>-0.2805</v>
       </c>
       <c r="G22" t="n">
         <v>-2.238</v>
@@ -2170,13 +2170,13 @@
         <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1806</v>
+        <v>-0.979</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.481</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3004</v>
+        <v>0.0124</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5744</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>J. FERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0451</v>
+        <v>-4.3403</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2337</v>
+        <v>-5.8055</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1887</v>
+        <v>1.4652</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1418</v>
+        <v>-3.9825</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.7269</v>
+        <v>-2.7536</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4149</v>
+        <v>-1.2289</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.4309</v>
+        <v>-3.833</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.1999</v>
+        <v>-2.6114</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.231</v>
+        <v>-1.2215</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2891</v>
+        <v>-0.1495</v>
       </c>
       <c r="N23" t="n">
-        <v>0.473</v>
+        <v>-0.1421</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.184</v>
+        <v>-0.0074</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.297</v>
+        <v>-3.891</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4087</v>
+        <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7638</v>
+        <v>-0.9</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3942</v>
+        <v>-0.9137</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3696</v>
+        <v>0.0136</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2512</v>
+        <v>2.5804</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8883</v>
+        <v>2.8321</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1395</v>
+        <v>-0.2518</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ HERNANDEZ</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5184</v>
+        <v>-4.4213</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0993</v>
+        <v>-4.7234</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5809</v>
+        <v>0.3021</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.9825</v>
+        <v>-4.1418</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7536</v>
+        <v>-2.7269</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2289</v>
+        <v>-1.4149</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.833</v>
+        <v>-4.4309</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.6114</v>
+        <v>-3.1999</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2215</v>
+        <v>-1.231</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1495</v>
+        <v>0.2891</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1421</v>
+        <v>0.473</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0074</v>
+        <v>-0.184</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.891</v>
+        <v>-1.297</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8529</v>
+        <v>2.4087</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0781</v>
+        <v>-1.14</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2074</v>
+        <v>-0.8838</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1293</v>
+        <v>-0.2562</v>
       </c>
       <c r="V24" t="n">
-        <v>2.5804</v>
+        <v>-0.2512</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8321</v>
+        <v>1.8883</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2518</v>
+        <v>-2.1395</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.83</v>
+        <v>-8.155900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3161</v>
+        <v>-8.0016</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5139</v>
+        <v>-0.1543</v>
       </c>
       <c r="G25" t="n">
         <v>-6.1413</v>
@@ -2404,13 +2404,13 @@
         <v>2.2234</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1781</v>
+        <v>-0.5039</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2077</v>
+        <v>-0.4778</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3858</v>
+        <v>-0.0261</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5106</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-24.5678</v>
+        <v>-23.2621</v>
       </c>
       <c r="E26" t="n">
-        <v>-28.1048</v>
+        <v>-28.1049</v>
       </c>
       <c r="F26" t="n">
-        <v>3.5373</v>
+        <v>4.8428</v>
       </c>
       <c r="G26" t="n">
         <v>-12.1564</v>
@@ -2482,19 +2482,19 @@
         <v>12.0437</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.337900000000001</v>
+        <v>-7.0321</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.75</v>
+        <v>-4.7502</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.5879</v>
+        <v>-2.2821</v>
       </c>
       <c r="V26" t="n">
         <v>-3.1471</v>
       </c>
       <c r="W26" t="n">
-        <v>6.292599999999999</v>
+        <v>6.2926</v>
       </c>
       <c r="X26" t="n">
         <v>-9.4398</v>
